--- a/import_class_top14.xlsx
+++ b/import_class_top14.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d41a2cc4a867f612/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6E8335A1-1EE3-4170-A752-85EB14B29C13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{6E8335A1-1EE3-4170-A752-85EB14B29C13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5620E72B-45C1-4754-BD98-9EFF927B4286}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{8408364A-AB56-463C-9617-C787E94273BF}"/>
   </bookViews>
@@ -25,10 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1435" uniqueCount="51">
-  <si>
-    <t>player</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1435" uniqueCount="50">
   <si>
     <t>block_key</t>
   </si>
@@ -40,9 +37,6 @@
   </si>
   <si>
     <t>winner_final</t>
-  </si>
-  <si>
-    <t>RCT</t>
   </si>
   <si>
     <t>Alexandre Collet</t>
@@ -96,19 +90,7 @@
     <t>Xavier</t>
   </si>
   <si>
-    <t>Kicker</t>
-  </si>
-  <si>
-    <t>Scoreur</t>
-  </si>
-  <si>
     <t>UBB</t>
-  </si>
-  <si>
-    <t>AB</t>
-  </si>
-  <si>
-    <t>ST</t>
   </si>
   <si>
     <t>Dréan</t>
@@ -121,9 +103,6 @@
   </si>
   <si>
     <t>Ramos</t>
-  </si>
-  <si>
-    <t>LBB</t>
   </si>
   <si>
     <t>Le Garrec</t>
@@ -141,43 +120,61 @@
     <t>Capuozzo</t>
   </si>
   <si>
-    <t>SR</t>
-  </si>
-  <si>
     <t>Le Brun</t>
   </si>
   <si>
     <t>all</t>
   </si>
   <si>
-    <t>ASM</t>
-  </si>
-  <si>
-    <t>R92</t>
-  </si>
-  <si>
-    <t>CO</t>
-  </si>
-  <si>
-    <t>SF</t>
-  </si>
-  <si>
-    <t>MHR</t>
-  </si>
-  <si>
-    <t>LOU</t>
-  </si>
-  <si>
     <t>Pau</t>
   </si>
   <si>
-    <t>USAP</t>
+    <t>player_name</t>
   </si>
   <si>
-    <t>USM</t>
+    <t>best_try_scorer</t>
   </si>
   <si>
-    <t>SO</t>
+    <t>best_point_scorer</t>
+  </si>
+  <si>
+    <t>Bielle-Biarrey</t>
+  </si>
+  <si>
+    <t>Toulouse</t>
+  </si>
+  <si>
+    <t>Toulon</t>
+  </si>
+  <si>
+    <t>Montauban</t>
+  </si>
+  <si>
+    <t>Clermont</t>
+  </si>
+  <si>
+    <t>Lyon</t>
+  </si>
+  <si>
+    <t>Castres</t>
+  </si>
+  <si>
+    <t>La Rochelle</t>
+  </si>
+  <si>
+    <t>Stade français</t>
+  </si>
+  <si>
+    <t>Racing 92</t>
+  </si>
+  <si>
+    <t>Perpignan</t>
+  </si>
+  <si>
+    <t>Montpellier</t>
+  </si>
+  <si>
+    <t>Bayonne</t>
   </si>
 </sst>
 </file>
@@ -299,7 +296,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="1" applyBorder="1"/>
@@ -308,7 +305,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -633,48 +629,48 @@
   <sheetData>
     <row r="1" spans="1:39" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
       <c r="F1" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="G1" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
     </row>
     <row r="2" spans="1:39" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="F2" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G2" s="8" t="s">
-        <v>31</v>
+      <c r="F2" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>25</v>
       </c>
       <c r="I2" s="1"/>
       <c r="K2" s="1"/>
@@ -709,25 +705,25 @@
     </row>
     <row r="3" spans="1:39" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F3" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G3" s="8" t="s">
-        <v>31</v>
+        <v>38</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>25</v>
       </c>
       <c r="I3" s="1"/>
       <c r="K3" s="2"/>
@@ -762,25 +758,25 @@
     </row>
     <row r="4" spans="1:39" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C4">
         <v>1</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F4" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G4" s="8" t="s">
-        <v>31</v>
+        <v>21</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>25</v>
       </c>
       <c r="I4" s="1"/>
       <c r="K4" s="2"/>
@@ -815,25 +811,25 @@
     </row>
     <row r="5" spans="1:39" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C5">
         <v>1</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="G5" s="8" t="s">
-        <v>29</v>
+        <v>38</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>23</v>
       </c>
       <c r="I5" s="1"/>
       <c r="K5" s="2"/>
@@ -868,25 +864,25 @@
     </row>
     <row r="6" spans="1:39" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C6">
         <v>1</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F6" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="G6" s="8" t="s">
-        <v>31</v>
+        <v>38</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>25</v>
       </c>
       <c r="I6" s="1"/>
       <c r="K6" s="2"/>
@@ -921,25 +917,25 @@
     </row>
     <row r="7" spans="1:39" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C7">
         <v>1</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F7" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G7" s="8" t="s">
-        <v>31</v>
+        <v>38</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>25</v>
       </c>
       <c r="I7" s="1"/>
       <c r="K7" s="6"/>
@@ -974,25 +970,25 @@
     </row>
     <row r="8" spans="1:39" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C8">
         <v>1</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F8" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G8" s="8" t="s">
-        <v>33</v>
+        <v>21</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>26</v>
       </c>
       <c r="I8" s="1"/>
       <c r="K8" s="1"/>
@@ -1027,25 +1023,25 @@
     </row>
     <row r="9" spans="1:39" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C9">
         <v>1</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>5</v>
+        <v>39</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F9" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="G9" s="8" t="s">
-        <v>34</v>
+        <v>39</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>27</v>
       </c>
       <c r="I9" s="1"/>
       <c r="K9" s="2"/>
@@ -1080,25 +1076,25 @@
     </row>
     <row r="10" spans="1:39" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C10">
         <v>1</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F10" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G10" s="4" t="s">
         <v>28</v>
-      </c>
-      <c r="G10" s="8" t="s">
-        <v>35</v>
       </c>
       <c r="I10" s="1"/>
       <c r="K10" s="2"/>
@@ -1133,25 +1129,25 @@
     </row>
     <row r="11" spans="1:39" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C11">
         <v>1</v>
       </c>
       <c r="D11" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G11" s="4" t="s">
         <v>27</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F11" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="G11" s="8" t="s">
-        <v>34</v>
       </c>
       <c r="I11" s="1"/>
       <c r="K11" s="2"/>
@@ -1186,25 +1182,25 @@
     </row>
     <row r="12" spans="1:39" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C12">
         <v>1</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F12" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G12" s="8" t="s">
-        <v>31</v>
+        <v>38</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>25</v>
       </c>
       <c r="I12" s="1"/>
       <c r="K12" s="2"/>
@@ -1239,25 +1235,25 @@
     </row>
     <row r="13" spans="1:39" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B13" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C13">
         <v>1</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F13" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="G13" s="8" t="s">
-        <v>35</v>
+        <v>38</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>28</v>
       </c>
       <c r="I13" s="1"/>
       <c r="K13" s="6"/>
@@ -1292,25 +1288,25 @@
     </row>
     <row r="14" spans="1:39" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B14" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C14">
         <v>1</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F14" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="G14" s="8" t="s">
-        <v>33</v>
+        <v>21</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>26</v>
       </c>
       <c r="I14" s="1"/>
       <c r="K14" s="1"/>
@@ -1345,25 +1341,25 @@
     </row>
     <row r="15" spans="1:39" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B15" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C15">
         <v>1</v>
       </c>
       <c r="D15" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G15" s="4" t="s">
         <v>27</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F15" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G15" s="8" t="s">
-        <v>34</v>
       </c>
       <c r="I15" s="1"/>
       <c r="K15" s="2"/>
@@ -1398,25 +1394,25 @@
     </row>
     <row r="16" spans="1:39" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B16" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C16">
         <v>1</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="F16" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="G16" s="8" t="s">
-        <v>39</v>
+        <v>44</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>31</v>
       </c>
       <c r="I16" s="1"/>
       <c r="K16" s="2"/>
@@ -1451,25 +1447,25 @@
     </row>
     <row r="17" spans="1:39" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B17" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C17">
         <v>1</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F17" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G17" s="8" t="s">
-        <v>35</v>
+        <v>38</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>28</v>
       </c>
       <c r="I17" s="1"/>
       <c r="K17" s="2"/>
@@ -1504,25 +1500,25 @@
     </row>
     <row r="18" spans="1:39" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B18" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C18">
         <v>1</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F18" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="G18" s="8" t="s">
-        <v>29</v>
+        <v>39</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>23</v>
       </c>
       <c r="I18" s="1"/>
       <c r="K18" s="2"/>
@@ -1557,10 +1553,10 @@
     </row>
     <row r="19" spans="1:39" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B19" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C19">
         <v>2</v>
@@ -1571,11 +1567,11 @@
       <c r="E19" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="F19" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G19" s="8" t="s">
-        <v>31</v>
+      <c r="F19" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>25</v>
       </c>
       <c r="I19" s="1"/>
       <c r="K19" s="6"/>
@@ -1610,25 +1606,25 @@
     </row>
     <row r="20" spans="1:39" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B20" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C20">
         <v>2</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F20" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G20" s="8" t="s">
-        <v>31</v>
+        <v>38</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>25</v>
       </c>
       <c r="I20" s="1"/>
       <c r="K20" s="1"/>
@@ -1663,25 +1659,25 @@
     </row>
     <row r="21" spans="1:39" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B21" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C21">
         <v>2</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F21" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G21" s="8" t="s">
-        <v>31</v>
+        <v>21</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>25</v>
       </c>
       <c r="I21" s="1"/>
       <c r="K21" s="2"/>
@@ -1716,25 +1712,25 @@
     </row>
     <row r="22" spans="1:39" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B22" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C22">
         <v>2</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F22" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="G22" s="8" t="s">
-        <v>29</v>
+        <v>38</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G22" s="4" t="s">
+        <v>23</v>
       </c>
       <c r="I22" s="1"/>
       <c r="K22" s="2"/>
@@ -1769,25 +1765,25 @@
     </row>
     <row r="23" spans="1:39" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B23" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C23">
         <v>2</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F23" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="G23" s="8" t="s">
-        <v>31</v>
+        <v>38</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G23" s="4" t="s">
+        <v>25</v>
       </c>
       <c r="I23" s="1"/>
       <c r="K23" s="2"/>
@@ -1822,25 +1818,25 @@
     </row>
     <row r="24" spans="1:39" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B24" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C24">
         <v>2</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F24" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G24" s="8" t="s">
-        <v>31</v>
+        <v>38</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G24" s="4" t="s">
+        <v>25</v>
       </c>
       <c r="I24" s="1"/>
       <c r="K24" s="2"/>
@@ -1875,25 +1871,25 @@
     </row>
     <row r="25" spans="1:39" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B25" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C25">
         <v>2</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F25" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G25" s="8" t="s">
-        <v>33</v>
+        <v>21</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G25" s="4" t="s">
+        <v>26</v>
       </c>
       <c r="I25" s="1"/>
       <c r="K25" s="6"/>
@@ -1928,263 +1924,263 @@
     </row>
     <row r="26" spans="1:39" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B26" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C26">
         <v>2</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F26" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="G26" s="8" t="s">
-        <v>34</v>
+        <v>39</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G26" s="4" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="27" spans="1:39" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B27" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C27">
         <v>2</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F27" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G27" s="4" t="s">
         <v>28</v>
-      </c>
-      <c r="G27" s="8" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="28" spans="1:39" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B28" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C28">
         <v>2</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E28" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G28" s="4" t="s">
         <v>27</v>
-      </c>
-      <c r="F28" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="G28" s="8" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="29" spans="1:39" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B29" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C29">
         <v>2</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F29" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G29" s="8" t="s">
-        <v>31</v>
+        <v>38</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G29" s="4" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="30" spans="1:39" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B30" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C30">
         <v>2</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F30" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="G30" s="8" t="s">
-        <v>35</v>
+        <v>38</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="G30" s="4" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="31" spans="1:39" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B31" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C31">
         <v>2</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F31" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="G31" s="8" t="s">
-        <v>33</v>
+        <v>21</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="G31" s="4" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="32" spans="1:39" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B32" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C32">
         <v>2</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E32" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G32" s="4" t="s">
         <v>27</v>
-      </c>
-      <c r="F32" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G32" s="8" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B33" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C33">
         <v>2</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="F33" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="G33" s="8" t="s">
-        <v>39</v>
+        <v>44</v>
+      </c>
+      <c r="F33" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G33" s="4" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B34" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C34">
         <v>2</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F34" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G34" s="8" t="s">
-        <v>35</v>
+        <v>38</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G34" s="4" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B35" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C35">
         <v>2</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F35" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="G35" s="8" t="s">
-        <v>29</v>
+        <v>39</v>
+      </c>
+      <c r="F35" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G35" s="4" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B36" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C36">
         <v>3</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E36" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="F36" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G36" s="8" t="s">
-        <v>31</v>
+      <c r="F36" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G36" s="4" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B37" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C37">
         <v>3</v>
@@ -2193,113 +2189,113 @@
         <v>41</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F37" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G37" s="8" t="s">
-        <v>31</v>
+        <v>38</v>
+      </c>
+      <c r="F37" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G37" s="4" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B38" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C38">
         <v>3</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>5</v>
+        <v>39</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F38" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G38" s="8" t="s">
-        <v>31</v>
+        <v>21</v>
+      </c>
+      <c r="F38" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G38" s="4" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="39" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B39" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C39">
         <v>3</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F39" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="G39" s="8" t="s">
-        <v>29</v>
+        <v>38</v>
+      </c>
+      <c r="F39" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G39" s="4" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B40" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C40">
         <v>3</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F40" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="G40" s="8" t="s">
-        <v>31</v>
+        <v>38</v>
+      </c>
+      <c r="F40" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G40" s="4" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="41" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B41" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C41">
         <v>3</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>5</v>
+        <v>39</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F41" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G41" s="8" t="s">
-        <v>31</v>
+        <v>38</v>
+      </c>
+      <c r="F41" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G41" s="4" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="42" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B42" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C42">
         <v>3</v>
@@ -2308,21 +2304,21 @@
         <v>41</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F42" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G42" s="8" t="s">
-        <v>33</v>
+        <v>21</v>
+      </c>
+      <c r="F42" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G42" s="4" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="43" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B43" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C43">
         <v>3</v>
@@ -2331,711 +2327,711 @@
         <v>41</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F43" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="G43" s="8" t="s">
-        <v>34</v>
+        <v>39</v>
+      </c>
+      <c r="F43" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G43" s="4" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="44" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B44" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C44">
         <v>3</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F44" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="F44" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G44" s="4" t="s">
         <v>28</v>
-      </c>
-      <c r="G44" s="8" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="45" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B45" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C45">
         <v>3</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>5</v>
+        <v>39</v>
       </c>
       <c r="E45" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F45" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G45" s="4" t="s">
         <v>27</v>
-      </c>
-      <c r="F45" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="G45" s="8" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="46" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B46" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C46">
         <v>3</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>5</v>
+        <v>39</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F46" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G46" s="8" t="s">
-        <v>31</v>
+        <v>38</v>
+      </c>
+      <c r="F46" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G46" s="4" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="47" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B47" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C47">
         <v>3</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F47" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="G47" s="8" t="s">
-        <v>35</v>
+        <v>38</v>
+      </c>
+      <c r="F47" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="G47" s="4" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="48" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B48" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C48">
         <v>3</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F48" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="G48" s="8" t="s">
-        <v>33</v>
+        <v>21</v>
+      </c>
+      <c r="F48" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="G48" s="4" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="49" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B49" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C49">
         <v>3</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>5</v>
+        <v>39</v>
       </c>
       <c r="E49" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F49" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G49" s="4" t="s">
         <v>27</v>
-      </c>
-      <c r="F49" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G49" s="8" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="50" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B50" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C50">
         <v>3</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="F50" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="G50" s="8" t="s">
-        <v>39</v>
+        <v>44</v>
+      </c>
+      <c r="F50" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G50" s="4" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="51" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B51" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C51">
         <v>3</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>5</v>
+        <v>39</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F51" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G51" s="8" t="s">
-        <v>35</v>
+        <v>38</v>
+      </c>
+      <c r="F51" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G51" s="4" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="52" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B52" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C52">
         <v>3</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F52" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="G52" s="8" t="s">
-        <v>29</v>
+        <v>39</v>
+      </c>
+      <c r="F52" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G52" s="4" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="53" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B53" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C53">
         <v>4</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="E53" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="F53" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G53" s="8" t="s">
-        <v>31</v>
+      <c r="F53" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G53" s="4" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="54" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B54" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C54">
         <v>4</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>5</v>
+        <v>39</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F54" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G54" s="8" t="s">
-        <v>31</v>
+        <v>38</v>
+      </c>
+      <c r="F54" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G54" s="4" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="55" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B55" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C55">
         <v>4</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F55" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G55" s="8" t="s">
-        <v>31</v>
+        <v>21</v>
+      </c>
+      <c r="F55" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G55" s="4" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="56" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B56" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C56">
         <v>4</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>5</v>
+        <v>39</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F56" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="G56" s="8" t="s">
-        <v>29</v>
+        <v>38</v>
+      </c>
+      <c r="F56" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G56" s="4" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="57" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B57" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C57">
         <v>4</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>5</v>
+        <v>39</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F57" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="G57" s="8" t="s">
-        <v>31</v>
+        <v>38</v>
+      </c>
+      <c r="F57" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G57" s="4" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="58" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B58" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C58">
         <v>4</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F58" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G58" s="8" t="s">
-        <v>31</v>
+        <v>38</v>
+      </c>
+      <c r="F58" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G58" s="4" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="59" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B59" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C59">
         <v>4</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>5</v>
+        <v>39</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F59" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G59" s="8" t="s">
-        <v>33</v>
+        <v>21</v>
+      </c>
+      <c r="F59" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G59" s="4" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="60" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B60" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C60">
         <v>4</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F60" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="G60" s="8" t="s">
-        <v>34</v>
+        <v>39</v>
+      </c>
+      <c r="F60" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G60" s="4" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="61" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B61" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C61">
         <v>4</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>5</v>
+        <v>39</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F61" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="F61" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G61" s="4" t="s">
         <v>28</v>
-      </c>
-      <c r="G61" s="8" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="62" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B62" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C62">
         <v>4</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="E62" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F62" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G62" s="4" t="s">
         <v>27</v>
-      </c>
-      <c r="F62" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="G62" s="8" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="63" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B63" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C63">
         <v>4</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F63" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G63" s="8" t="s">
-        <v>31</v>
+        <v>38</v>
+      </c>
+      <c r="F63" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G63" s="4" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="64" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B64" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C64">
         <v>4</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>5</v>
+        <v>39</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F64" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="G64" s="8" t="s">
-        <v>35</v>
+        <v>38</v>
+      </c>
+      <c r="F64" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="G64" s="4" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="65" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B65" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C65">
         <v>4</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>5</v>
+        <v>39</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F65" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="G65" s="8" t="s">
-        <v>33</v>
+        <v>21</v>
+      </c>
+      <c r="F65" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="G65" s="4" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="66" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B66" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C66">
         <v>4</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="E66" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F66" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G66" s="4" t="s">
         <v>27</v>
-      </c>
-      <c r="F66" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G66" s="8" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="67" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B67" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C67">
         <v>4</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>5</v>
+        <v>39</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="F67" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="G67" s="8" t="s">
-        <v>39</v>
+        <v>44</v>
+      </c>
+      <c r="F67" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G67" s="4" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="68" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B68" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C68">
         <v>4</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F68" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G68" s="8" t="s">
-        <v>35</v>
+        <v>38</v>
+      </c>
+      <c r="F68" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G68" s="4" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="69" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B69" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C69">
         <v>4</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>5</v>
+        <v>39</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F69" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="G69" s="8" t="s">
-        <v>29</v>
+        <v>39</v>
+      </c>
+      <c r="F69" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G69" s="4" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="70" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B70" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C70">
         <v>5</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="E70" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="F70" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G70" s="8" t="s">
-        <v>31</v>
+      <c r="F70" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G70" s="4" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="71" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B71" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C71">
         <v>5</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F71" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G71" s="8" t="s">
-        <v>31</v>
+        <v>38</v>
+      </c>
+      <c r="F71" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G71" s="4" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="72" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B72" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C72">
         <v>5</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F72" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G72" s="8" t="s">
-        <v>31</v>
+        <v>21</v>
+      </c>
+      <c r="F72" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G72" s="4" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="73" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B73" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C73">
         <v>5</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F73" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="G73" s="8" t="s">
-        <v>29</v>
+        <v>38</v>
+      </c>
+      <c r="F73" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G73" s="4" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="74" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B74" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C74">
         <v>5</v>
@@ -3044,22 +3040,22 @@
         <v>41</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F74" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="G74" s="8" t="s">
-        <v>31</v>
+        <v>38</v>
+      </c>
+      <c r="F74" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G74" s="4" t="s">
+        <v>25</v>
       </c>
       <c r="I74" s="4"/>
     </row>
     <row r="75" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B75" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C75">
         <v>5</v>
@@ -3068,21 +3064,21 @@
         <v>43</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F75" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G75" s="8" t="s">
-        <v>31</v>
+        <v>38</v>
+      </c>
+      <c r="F75" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G75" s="4" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="76" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B76" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C76">
         <v>5</v>
@@ -3091,44 +3087,44 @@
         <v>43</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F76" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G76" s="8" t="s">
-        <v>33</v>
+        <v>21</v>
+      </c>
+      <c r="F76" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G76" s="4" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="77" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B77" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C77">
         <v>5</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F77" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="G77" s="8" t="s">
-        <v>34</v>
+        <v>39</v>
+      </c>
+      <c r="F77" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G77" s="4" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="78" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B78" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C78">
         <v>5</v>
@@ -3137,21 +3133,21 @@
         <v>41</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F78" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="F78" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G78" s="4" t="s">
         <v>28</v>
-      </c>
-      <c r="G78" s="8" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="79" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B79" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C79">
         <v>5</v>
@@ -3160,21 +3156,21 @@
         <v>43</v>
       </c>
       <c r="E79" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F79" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G79" s="4" t="s">
         <v>27</v>
-      </c>
-      <c r="F79" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="G79" s="8" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="80" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B80" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C80">
         <v>5</v>
@@ -3183,90 +3179,90 @@
         <v>41</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F80" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G80" s="8" t="s">
-        <v>31</v>
+        <v>38</v>
+      </c>
+      <c r="F80" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G80" s="4" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="81" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B81" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C81">
         <v>5</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F81" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="G81" s="8" t="s">
-        <v>35</v>
+        <v>38</v>
+      </c>
+      <c r="F81" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="G81" s="4" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="82" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B82" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C82">
         <v>5</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F82" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="G82" s="8" t="s">
-        <v>33</v>
+        <v>21</v>
+      </c>
+      <c r="F82" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="G82" s="4" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="83" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B83" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C83">
         <v>5</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="E83" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F83" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G83" s="4" t="s">
         <v>27</v>
-      </c>
-      <c r="F83" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G83" s="8" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="84" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B84" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C84">
         <v>5</v>
@@ -3275,21 +3271,21 @@
         <v>41</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="F84" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="G84" s="8" t="s">
-        <v>39</v>
+        <v>44</v>
+      </c>
+      <c r="F84" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G84" s="4" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="85" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B85" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C85">
         <v>5</v>
@@ -3298,113 +3294,113 @@
         <v>43</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F85" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G85" s="8" t="s">
-        <v>35</v>
+        <v>38</v>
+      </c>
+      <c r="F85" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G85" s="4" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="86" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B86" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C86">
         <v>5</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F86" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="G86" s="8" t="s">
-        <v>29</v>
+        <v>39</v>
+      </c>
+      <c r="F86" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G86" s="4" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="87" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B87" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C87">
         <v>6</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>5</v>
+        <v>39</v>
       </c>
       <c r="E87" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="F87" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G87" s="8" t="s">
-        <v>31</v>
+      <c r="F87" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G87" s="4" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="88" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B88" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C88">
         <v>6</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F88" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G88" s="8" t="s">
-        <v>31</v>
+        <v>38</v>
+      </c>
+      <c r="F88" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G88" s="4" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="89" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B89" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C89">
         <v>6</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F89" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G89" s="8" t="s">
-        <v>31</v>
+        <v>21</v>
+      </c>
+      <c r="F89" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G89" s="4" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="90" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B90" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C90">
         <v>6</v>
@@ -3413,44 +3409,44 @@
         <v>41</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F90" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="G90" s="8" t="s">
-        <v>29</v>
+        <v>38</v>
+      </c>
+      <c r="F90" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G90" s="4" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="91" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B91" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C91">
         <v>6</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F91" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="G91" s="8" t="s">
-        <v>31</v>
+        <v>38</v>
+      </c>
+      <c r="F91" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G91" s="4" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="92" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B92" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C92">
         <v>6</v>
@@ -3459,67 +3455,67 @@
         <v>41</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F92" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G92" s="8" t="s">
-        <v>31</v>
+        <v>38</v>
+      </c>
+      <c r="F92" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G92" s="4" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="93" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B93" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C93">
         <v>6</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F93" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G93" s="8" t="s">
-        <v>33</v>
+        <v>21</v>
+      </c>
+      <c r="F93" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G93" s="4" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="94" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B94" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C94">
         <v>6</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F94" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="G94" s="8" t="s">
-        <v>34</v>
+        <v>39</v>
+      </c>
+      <c r="F94" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G94" s="4" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="95" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B95" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C95">
         <v>6</v>
@@ -3528,21 +3524,21 @@
         <v>43</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F95" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="F95" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G95" s="4" t="s">
         <v>28</v>
-      </c>
-      <c r="G95" s="8" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="96" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B96" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C96">
         <v>6</v>
@@ -3551,44 +3547,44 @@
         <v>41</v>
       </c>
       <c r="E96" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F96" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G96" s="4" t="s">
         <v>27</v>
-      </c>
-      <c r="F96" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="G96" s="8" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="97" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B97" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C97">
         <v>6</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F97" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G97" s="8" t="s">
-        <v>31</v>
+        <v>38</v>
+      </c>
+      <c r="F97" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G97" s="4" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="98" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B98" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C98">
         <v>6</v>
@@ -3597,44 +3593,44 @@
         <v>41</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F98" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="G98" s="8" t="s">
-        <v>35</v>
+        <v>38</v>
+      </c>
+      <c r="F98" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="G98" s="4" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="99" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B99" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C99">
         <v>6</v>
       </c>
       <c r="D99" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E99" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F99" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="G99" s="4" t="s">
         <v>26</v>
-      </c>
-      <c r="E99" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F99" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="G99" s="8" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="100" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B100" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C100">
         <v>6</v>
@@ -3643,21 +3639,21 @@
         <v>41</v>
       </c>
       <c r="E100" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F100" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G100" s="4" t="s">
         <v>27</v>
-      </c>
-      <c r="F100" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G100" s="8" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="101" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B101" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C101">
         <v>6</v>
@@ -3666,21 +3662,21 @@
         <v>43</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="F101" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="G101" s="8" t="s">
-        <v>39</v>
+        <v>44</v>
+      </c>
+      <c r="F101" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G101" s="4" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="102" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B102" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C102">
         <v>6</v>
@@ -3689,21 +3685,21 @@
         <v>41</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F102" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G102" s="8" t="s">
-        <v>35</v>
+        <v>38</v>
+      </c>
+      <c r="F102" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G102" s="4" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="103" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B103" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C103">
         <v>6</v>
@@ -3712,21 +3708,21 @@
         <v>43</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F103" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="G103" s="8" t="s">
-        <v>29</v>
+        <v>39</v>
+      </c>
+      <c r="F103" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G103" s="4" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="104" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B104" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C104">
         <v>7</v>
@@ -3737,42 +3733,42 @@
       <c r="E104" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="F104" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G104" s="8" t="s">
-        <v>31</v>
+      <c r="F104" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G104" s="4" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="105" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B105" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C105">
         <v>7</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F105" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G105" s="8" t="s">
-        <v>31</v>
+        <v>38</v>
+      </c>
+      <c r="F105" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G105" s="4" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="106" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B106" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C106">
         <v>7</v>
@@ -3781,44 +3777,44 @@
         <v>43</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F106" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G106" s="8" t="s">
-        <v>31</v>
+        <v>21</v>
+      </c>
+      <c r="F106" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G106" s="4" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="107" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B107" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C107">
         <v>7</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F107" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="G107" s="8" t="s">
-        <v>29</v>
+        <v>38</v>
+      </c>
+      <c r="F107" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G107" s="4" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="108" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B108" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C108">
         <v>7</v>
@@ -3827,136 +3823,136 @@
         <v>43</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F108" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="G108" s="8" t="s">
-        <v>31</v>
+        <v>38</v>
+      </c>
+      <c r="F108" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G108" s="4" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="109" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B109" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C109">
         <v>7</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F109" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G109" s="8" t="s">
-        <v>31</v>
+        <v>38</v>
+      </c>
+      <c r="F109" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G109" s="4" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="110" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B110" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C110">
         <v>7</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F110" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G110" s="8" t="s">
-        <v>33</v>
+        <v>21</v>
+      </c>
+      <c r="F110" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G110" s="4" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="111" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B111" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C111">
         <v>7</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F111" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="G111" s="8" t="s">
-        <v>34</v>
+        <v>39</v>
+      </c>
+      <c r="F111" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G111" s="4" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="112" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B112" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C112">
         <v>7</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F112" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="F112" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G112" s="4" t="s">
         <v>28</v>
-      </c>
-      <c r="G112" s="8" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="113" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B113" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C113">
         <v>7</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="E113" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F113" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G113" s="4" t="s">
         <v>27</v>
-      </c>
-      <c r="F113" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="G113" s="8" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="114" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B114" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C114">
         <v>7</v>
@@ -3965,136 +3961,136 @@
         <v>43</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F114" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G114" s="8" t="s">
-        <v>31</v>
+        <v>38</v>
+      </c>
+      <c r="F114" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G114" s="4" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="115" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B115" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C115">
         <v>7</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F115" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="G115" s="8" t="s">
-        <v>35</v>
+        <v>38</v>
+      </c>
+      <c r="F115" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="G115" s="4" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="116" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B116" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C116">
         <v>7</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F116" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="G116" s="8" t="s">
-        <v>33</v>
+        <v>21</v>
+      </c>
+      <c r="F116" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="G116" s="4" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="117" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B117" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C117">
         <v>7</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E117" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F117" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G117" s="4" t="s">
         <v>27</v>
-      </c>
-      <c r="F117" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G117" s="8" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="118" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B118" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C118">
         <v>7</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="F118" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="G118" s="8" t="s">
-        <v>39</v>
+        <v>44</v>
+      </c>
+      <c r="F118" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G118" s="4" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="119" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B119" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C119">
         <v>7</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F119" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G119" s="8" t="s">
-        <v>35</v>
+        <v>38</v>
+      </c>
+      <c r="F119" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G119" s="4" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="120" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B120" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C120">
         <v>7</v>
@@ -4103,297 +4099,297 @@
         <v>41</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F120" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="G120" s="8" t="s">
-        <v>29</v>
+        <v>39</v>
+      </c>
+      <c r="F120" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G120" s="4" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="121" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B121" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C121">
         <v>8</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E121" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="F121" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G121" s="8" t="s">
-        <v>31</v>
+      <c r="F121" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G121" s="4" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="122" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B122" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C122">
         <v>8</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F122" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G122" s="8" t="s">
-        <v>31</v>
+        <v>38</v>
+      </c>
+      <c r="F122" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G122" s="4" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="123" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B123" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C123">
         <v>8</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F123" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G123" s="8" t="s">
-        <v>31</v>
+        <v>21</v>
+      </c>
+      <c r="F123" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G123" s="4" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="124" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B124" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C124">
         <v>8</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F124" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="G124" s="8" t="s">
-        <v>29</v>
+        <v>38</v>
+      </c>
+      <c r="F124" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G124" s="4" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="125" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B125" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C125">
         <v>8</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F125" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="G125" s="8" t="s">
-        <v>31</v>
+        <v>38</v>
+      </c>
+      <c r="F125" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G125" s="4" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="126" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B126" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C126">
         <v>8</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F126" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G126" s="8" t="s">
-        <v>31</v>
+        <v>38</v>
+      </c>
+      <c r="F126" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G126" s="4" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="127" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B127" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C127">
         <v>8</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F127" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G127" s="8" t="s">
-        <v>33</v>
+        <v>21</v>
+      </c>
+      <c r="F127" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G127" s="4" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="128" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B128" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C128">
         <v>8</v>
       </c>
       <c r="D128" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E128" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F128" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G128" s="4" t="s">
         <v>27</v>
-      </c>
-      <c r="E128" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F128" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="G128" s="8" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="129" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B129" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C129">
         <v>8</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F129" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="F129" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G129" s="4" t="s">
         <v>28</v>
-      </c>
-      <c r="G129" s="8" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="130" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B130" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C130">
         <v>8</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="E130" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F130" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G130" s="4" t="s">
         <v>27</v>
-      </c>
-      <c r="F130" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="G130" s="8" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="131" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B131" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C131">
         <v>8</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F131" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G131" s="8" t="s">
-        <v>31</v>
+        <v>38</v>
+      </c>
+      <c r="F131" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G131" s="4" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="132" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B132" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C132">
         <v>8</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F132" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="G132" s="8" t="s">
-        <v>35</v>
+        <v>38</v>
+      </c>
+      <c r="F132" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="G132" s="4" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="133" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B133" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C133">
         <v>8</v>
@@ -4402,136 +4398,136 @@
         <v>43</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F133" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="G133" s="8" t="s">
-        <v>33</v>
+        <v>21</v>
+      </c>
+      <c r="F133" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="G133" s="4" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="134" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B134" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C134">
         <v>8</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="E134" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F134" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G134" s="4" t="s">
         <v>27</v>
-      </c>
-      <c r="F134" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G134" s="8" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="135" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B135" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C135">
         <v>8</v>
       </c>
       <c r="D135" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E135" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="F135" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="E135" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="F135" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="G135" s="8" t="s">
-        <v>39</v>
+      <c r="G135" s="4" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="136" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B136" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C136">
         <v>8</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F136" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G136" s="8" t="s">
-        <v>35</v>
+        <v>38</v>
+      </c>
+      <c r="F136" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G136" s="4" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="137" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B137" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C137">
         <v>8</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F137" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="G137" s="8" t="s">
-        <v>29</v>
+        <v>39</v>
+      </c>
+      <c r="F137" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G137" s="4" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="138" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B138" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C138">
         <v>9</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E138" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="F138" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G138" s="8" t="s">
-        <v>31</v>
+      <c r="F138" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G138" s="4" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="139" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B139" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C139">
         <v>9</v>
@@ -4540,136 +4536,136 @@
         <v>43</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F139" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G139" s="8" t="s">
-        <v>31</v>
+        <v>38</v>
+      </c>
+      <c r="F139" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G139" s="4" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="140" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B140" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C140">
         <v>9</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F140" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G140" s="8" t="s">
-        <v>31</v>
+        <v>21</v>
+      </c>
+      <c r="F140" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G140" s="4" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="141" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B141" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C141">
         <v>9</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F141" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="G141" s="8" t="s">
-        <v>29</v>
+        <v>38</v>
+      </c>
+      <c r="F141" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G141" s="4" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="142" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B142" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C142">
         <v>9</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F142" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="G142" s="8" t="s">
-        <v>31</v>
+        <v>38</v>
+      </c>
+      <c r="F142" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G142" s="4" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="143" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B143" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C143">
         <v>9</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F143" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G143" s="8" t="s">
-        <v>31</v>
+        <v>38</v>
+      </c>
+      <c r="F143" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G143" s="4" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="144" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B144" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C144">
         <v>9</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F144" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G144" s="8" t="s">
-        <v>33</v>
+        <v>21</v>
+      </c>
+      <c r="F144" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G144" s="4" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="145" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B145" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C145">
         <v>9</v>
@@ -4678,90 +4674,90 @@
         <v>43</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F145" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="G145" s="8" t="s">
-        <v>34</v>
+        <v>39</v>
+      </c>
+      <c r="F145" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G145" s="4" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="146" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B146" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C146">
         <v>9</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F146" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="F146" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G146" s="4" t="s">
         <v>28</v>
-      </c>
-      <c r="G146" s="8" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="147" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B147" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C147">
         <v>9</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="E147" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F147" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G147" s="4" t="s">
         <v>27</v>
-      </c>
-      <c r="F147" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="G147" s="8" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="148" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B148" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C148">
         <v>9</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F148" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G148" s="8" t="s">
-        <v>31</v>
+        <v>38</v>
+      </c>
+      <c r="F148" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G148" s="4" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="149" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B149" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C149">
         <v>9</v>
@@ -4770,412 +4766,412 @@
         <v>43</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F149" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="G149" s="8" t="s">
-        <v>35</v>
+        <v>38</v>
+      </c>
+      <c r="F149" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="G149" s="4" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="150" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B150" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C150">
         <v>9</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F150" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="G150" s="8" t="s">
-        <v>33</v>
+        <v>21</v>
+      </c>
+      <c r="F150" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="G150" s="4" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="151" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B151" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C151">
         <v>9</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E151" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F151" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G151" s="4" t="s">
         <v>27</v>
-      </c>
-      <c r="F151" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G151" s="8" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="152" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B152" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C152">
         <v>9</v>
       </c>
       <c r="D152" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E152" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="E152" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="F152" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="G152" s="8" t="s">
-        <v>39</v>
+      <c r="F152" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G152" s="4" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="153" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B153" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C153">
         <v>9</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F153" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G153" s="8" t="s">
-        <v>35</v>
+        <v>38</v>
+      </c>
+      <c r="F153" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G153" s="4" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="154" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B154" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C154">
         <v>9</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F154" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="G154" s="8" t="s">
-        <v>29</v>
+        <v>39</v>
+      </c>
+      <c r="F154" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G154" s="4" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="155" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B155" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C155">
         <v>10</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="E155" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="F155" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G155" s="8" t="s">
-        <v>31</v>
+      <c r="F155" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G155" s="4" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="156" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B156" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C156">
         <v>10</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F156" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G156" s="8" t="s">
-        <v>31</v>
+        <v>38</v>
+      </c>
+      <c r="F156" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G156" s="4" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="157" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B157" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C157">
         <v>10</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F157" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G157" s="8" t="s">
-        <v>31</v>
+        <v>21</v>
+      </c>
+      <c r="F157" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G157" s="4" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="158" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B158" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C158">
         <v>10</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F158" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="G158" s="8" t="s">
-        <v>29</v>
+        <v>38</v>
+      </c>
+      <c r="F158" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G158" s="4" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="159" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B159" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C159">
         <v>10</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F159" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="G159" s="8" t="s">
-        <v>31</v>
+        <v>38</v>
+      </c>
+      <c r="F159" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G159" s="4" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="160" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B160" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C160">
         <v>10</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F160" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G160" s="8" t="s">
-        <v>31</v>
+        <v>38</v>
+      </c>
+      <c r="F160" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G160" s="4" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="161" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B161" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C161">
         <v>10</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F161" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G161" s="8" t="s">
-        <v>33</v>
+        <v>21</v>
+      </c>
+      <c r="F161" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G161" s="4" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="162" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B162" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C162">
         <v>10</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F162" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="G162" s="8" t="s">
-        <v>34</v>
+        <v>39</v>
+      </c>
+      <c r="F162" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G162" s="4" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="163" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B163" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C163">
         <v>10</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F163" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="F163" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G163" s="4" t="s">
         <v>28</v>
-      </c>
-      <c r="G163" s="8" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="164" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B164" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C164">
         <v>10</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="E164" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F164" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G164" s="4" t="s">
         <v>27</v>
-      </c>
-      <c r="F164" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="G164" s="8" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="165" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B165" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C165">
         <v>10</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F165" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G165" s="8" t="s">
-        <v>31</v>
+        <v>38</v>
+      </c>
+      <c r="F165" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G165" s="4" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="166" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B166" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C166">
         <v>10</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F166" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="G166" s="8" t="s">
-        <v>35</v>
+        <v>38</v>
+      </c>
+      <c r="F166" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="G166" s="4" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="167" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B167" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C167">
         <v>10</v>
@@ -5184,159 +5180,159 @@
         <v>41</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F167" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="G167" s="8" t="s">
-        <v>33</v>
+        <v>21</v>
+      </c>
+      <c r="F167" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="G167" s="4" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="168" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B168" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C168">
         <v>10</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="E168" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F168" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G168" s="4" t="s">
         <v>27</v>
-      </c>
-      <c r="F168" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G168" s="8" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="169" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B169" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C169">
         <v>10</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="F169" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="G169" s="8" t="s">
-        <v>39</v>
+        <v>44</v>
+      </c>
+      <c r="F169" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G169" s="4" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="170" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B170" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C170">
         <v>10</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F170" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G170" s="8" t="s">
-        <v>35</v>
+        <v>38</v>
+      </c>
+      <c r="F170" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G170" s="4" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="171" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B171" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C171">
         <v>10</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F171" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="G171" s="8" t="s">
-        <v>29</v>
+        <v>39</v>
+      </c>
+      <c r="F171" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G171" s="4" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="172" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B172" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C172">
         <v>11</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="E172" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="F172" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G172" s="8" t="s">
-        <v>31</v>
+      <c r="F172" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G172" s="4" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="173" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B173" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C173">
         <v>11</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F173" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G173" s="8" t="s">
-        <v>31</v>
+        <v>38</v>
+      </c>
+      <c r="F173" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G173" s="4" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="174" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B174" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C174">
         <v>11</v>
@@ -5345,21 +5341,21 @@
         <v>41</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F174" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G174" s="8" t="s">
-        <v>31</v>
+        <v>21</v>
+      </c>
+      <c r="F174" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G174" s="4" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="175" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B175" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C175">
         <v>11</v>
@@ -5368,2506 +5364,2506 @@
         <v>43</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F175" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="G175" s="8" t="s">
-        <v>29</v>
+        <v>38</v>
+      </c>
+      <c r="F175" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G175" s="4" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="176" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B176" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C176">
         <v>11</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F176" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="G176" s="8" t="s">
-        <v>31</v>
+        <v>38</v>
+      </c>
+      <c r="F176" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G176" s="4" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="177" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B177" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C177">
         <v>11</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F177" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G177" s="8" t="s">
-        <v>31</v>
+        <v>38</v>
+      </c>
+      <c r="F177" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G177" s="4" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="178" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B178" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C178">
         <v>11</v>
       </c>
       <c r="D178" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E178" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F178" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G178" s="4" t="s">
         <v>26</v>
-      </c>
-      <c r="E178" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F178" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G178" s="8" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="179" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B179" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C179">
         <v>11</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F179" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="G179" s="8" t="s">
-        <v>34</v>
+        <v>39</v>
+      </c>
+      <c r="F179" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G179" s="4" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="180" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B180" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C180">
         <v>11</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F180" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="F180" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G180" s="4" t="s">
         <v>28</v>
-      </c>
-      <c r="G180" s="8" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="181" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B181" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C181">
         <v>11</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E181" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F181" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G181" s="4" t="s">
         <v>27</v>
-      </c>
-      <c r="F181" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="G181" s="8" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="182" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B182" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C182">
         <v>11</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F182" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G182" s="8" t="s">
-        <v>31</v>
+        <v>38</v>
+      </c>
+      <c r="F182" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G182" s="4" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="183" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B183" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C183">
         <v>11</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F183" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="G183" s="8" t="s">
-        <v>35</v>
+        <v>38</v>
+      </c>
+      <c r="F183" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="G183" s="4" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="184" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B184" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C184">
         <v>11</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F184" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="G184" s="8" t="s">
-        <v>33</v>
+        <v>21</v>
+      </c>
+      <c r="F184" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="G184" s="4" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="185" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B185" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C185">
         <v>11</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="E185" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F185" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G185" s="4" t="s">
         <v>27</v>
-      </c>
-      <c r="F185" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G185" s="8" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="186" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B186" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C186">
         <v>11</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="F186" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="G186" s="8" t="s">
-        <v>39</v>
+        <v>44</v>
+      </c>
+      <c r="F186" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G186" s="4" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="187" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B187" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C187">
         <v>11</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F187" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G187" s="8" t="s">
-        <v>35</v>
+        <v>38</v>
+      </c>
+      <c r="F187" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G187" s="4" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="188" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B188" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C188">
         <v>11</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F188" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="G188" s="8" t="s">
-        <v>29</v>
+        <v>39</v>
+      </c>
+      <c r="F188" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G188" s="4" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="189" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B189" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C189">
         <v>12</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="E189" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="F189" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G189" s="8" t="s">
-        <v>31</v>
+      <c r="F189" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G189" s="4" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="190" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B190" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C190">
         <v>12</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F190" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G190" s="8" t="s">
-        <v>31</v>
+        <v>38</v>
+      </c>
+      <c r="F190" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G190" s="4" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="191" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B191" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C191">
         <v>12</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F191" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G191" s="8" t="s">
-        <v>31</v>
+        <v>21</v>
+      </c>
+      <c r="F191" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G191" s="4" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="192" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B192" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C192">
         <v>12</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F192" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="G192" s="8" t="s">
-        <v>29</v>
+        <v>38</v>
+      </c>
+      <c r="F192" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G192" s="4" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="193" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B193" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C193">
         <v>12</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F193" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="G193" s="8" t="s">
-        <v>31</v>
+        <v>38</v>
+      </c>
+      <c r="F193" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G193" s="4" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="194" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B194" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C194">
         <v>12</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F194" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G194" s="8" t="s">
-        <v>31</v>
+        <v>38</v>
+      </c>
+      <c r="F194" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G194" s="4" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="195" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B195" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C195">
         <v>12</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F195" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G195" s="8" t="s">
-        <v>33</v>
+        <v>21</v>
+      </c>
+      <c r="F195" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G195" s="4" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="196" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B196" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C196">
         <v>12</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F196" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="G196" s="8" t="s">
-        <v>34</v>
+        <v>39</v>
+      </c>
+      <c r="F196" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G196" s="4" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="197" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B197" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C197">
         <v>12</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F197" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="F197" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G197" s="4" t="s">
         <v>28</v>
-      </c>
-      <c r="G197" s="8" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="198" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B198" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C198">
         <v>12</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E198" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F198" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G198" s="4" t="s">
         <v>27</v>
-      </c>
-      <c r="F198" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="G198" s="8" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="199" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B199" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C199">
         <v>12</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F199" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G199" s="8" t="s">
-        <v>31</v>
+        <v>38</v>
+      </c>
+      <c r="F199" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G199" s="4" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="200" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B200" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C200">
         <v>12</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F200" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="G200" s="8" t="s">
-        <v>35</v>
+        <v>38</v>
+      </c>
+      <c r="F200" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="G200" s="4" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="201" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B201" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C201">
         <v>12</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F201" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="G201" s="8" t="s">
-        <v>33</v>
+        <v>21</v>
+      </c>
+      <c r="F201" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="G201" s="4" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="202" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B202" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C202">
         <v>12</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="E202" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F202" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G202" s="4" t="s">
         <v>27</v>
-      </c>
-      <c r="F202" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G202" s="8" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="203" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B203" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C203">
         <v>12</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="F203" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="G203" s="8" t="s">
-        <v>39</v>
+        <v>44</v>
+      </c>
+      <c r="F203" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G203" s="4" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="204" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B204" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C204">
         <v>12</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F204" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G204" s="8" t="s">
-        <v>35</v>
+        <v>38</v>
+      </c>
+      <c r="F204" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G204" s="4" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="205" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B205" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C205">
         <v>12</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F205" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="G205" s="8" t="s">
-        <v>29</v>
+        <v>39</v>
+      </c>
+      <c r="F205" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G205" s="4" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="206" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B206" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C206">
         <v>13</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E206" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="F206" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G206" s="8" t="s">
-        <v>31</v>
+      <c r="F206" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G206" s="4" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="207" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B207" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C207">
         <v>13</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E207" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F207" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G207" s="8" t="s">
-        <v>31</v>
+        <v>38</v>
+      </c>
+      <c r="F207" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G207" s="4" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="208" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B208" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C208">
         <v>13</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="E208" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F208" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G208" s="8" t="s">
-        <v>31</v>
+        <v>21</v>
+      </c>
+      <c r="F208" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G208" s="4" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="209" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A209" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B209" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C209">
         <v>13</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F209" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="G209" s="8" t="s">
-        <v>29</v>
+        <v>38</v>
+      </c>
+      <c r="F209" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G209" s="4" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="210" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B210" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C210">
         <v>13</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E210" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F210" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="G210" s="8" t="s">
-        <v>31</v>
+        <v>38</v>
+      </c>
+      <c r="F210" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G210" s="4" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="211" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B211" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C211">
         <v>13</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E211" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F211" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G211" s="8" t="s">
-        <v>31</v>
+        <v>38</v>
+      </c>
+      <c r="F211" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G211" s="4" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="212" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A212" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B212" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C212">
         <v>13</v>
       </c>
       <c r="D212" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E212" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F212" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G212" s="8" t="s">
-        <v>33</v>
+        <v>21</v>
+      </c>
+      <c r="F212" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G212" s="4" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="213" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A213" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B213" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C213">
         <v>13</v>
       </c>
       <c r="D213" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E213" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F213" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="G213" s="8" t="s">
-        <v>34</v>
+        <v>39</v>
+      </c>
+      <c r="F213" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G213" s="4" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="214" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A214" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B214" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C214">
         <v>13</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F214" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="F214" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G214" s="4" t="s">
         <v>28</v>
-      </c>
-      <c r="G214" s="8" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="215" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B215" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C215">
         <v>13</v>
       </c>
       <c r="D215" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E215" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F215" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G215" s="4" t="s">
         <v>27</v>
-      </c>
-      <c r="F215" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="G215" s="8" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="216" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A216" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B216" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C216">
         <v>13</v>
       </c>
       <c r="D216" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E216" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F216" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G216" s="8" t="s">
-        <v>31</v>
+        <v>38</v>
+      </c>
+      <c r="F216" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G216" s="4" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="217" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A217" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B217" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C217">
         <v>13</v>
       </c>
       <c r="D217" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E217" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F217" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="G217" s="8" t="s">
-        <v>35</v>
+        <v>38</v>
+      </c>
+      <c r="F217" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="G217" s="4" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="218" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A218" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B218" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C218">
         <v>13</v>
       </c>
       <c r="D218" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E218" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F218" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="G218" s="8" t="s">
-        <v>33</v>
+        <v>21</v>
+      </c>
+      <c r="F218" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="G218" s="4" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="219" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A219" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B219" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C219">
         <v>13</v>
       </c>
       <c r="D219" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E219" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F219" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G219" s="4" t="s">
         <v>27</v>
-      </c>
-      <c r="F219" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G219" s="8" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="220" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B220" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C220">
         <v>13</v>
       </c>
       <c r="D220" s="1" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="E220" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="F220" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="G220" s="8" t="s">
-        <v>39</v>
+        <v>44</v>
+      </c>
+      <c r="F220" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G220" s="4" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="221" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B221" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C221">
         <v>13</v>
       </c>
       <c r="D221" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E221" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F221" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G221" s="8" t="s">
-        <v>35</v>
+        <v>38</v>
+      </c>
+      <c r="F221" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G221" s="4" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="222" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B222" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C222">
         <v>13</v>
       </c>
       <c r="D222" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E222" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F222" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="G222" s="8" t="s">
-        <v>29</v>
+        <v>39</v>
+      </c>
+      <c r="F222" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G222" s="4" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="223" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B223" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C223">
         <v>14</v>
       </c>
       <c r="D223" s="1" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="E223" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="F223" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G223" s="8" t="s">
-        <v>31</v>
+      <c r="F223" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G223" s="4" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="224" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B224" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C224">
         <v>14</v>
       </c>
       <c r="D224" s="1" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="E224" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F224" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G224" s="8" t="s">
-        <v>31</v>
+        <v>38</v>
+      </c>
+      <c r="F224" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G224" s="4" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="225" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B225" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C225">
         <v>14</v>
       </c>
       <c r="D225" s="1" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="E225" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F225" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G225" s="8" t="s">
-        <v>31</v>
+        <v>21</v>
+      </c>
+      <c r="F225" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G225" s="4" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="226" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B226" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C226">
         <v>14</v>
       </c>
       <c r="D226" s="1" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="E226" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F226" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="G226" s="8" t="s">
-        <v>29</v>
+        <v>38</v>
+      </c>
+      <c r="F226" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G226" s="4" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="227" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B227" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C227">
         <v>14</v>
       </c>
       <c r="D227" s="1" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="E227" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F227" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="G227" s="8" t="s">
-        <v>31</v>
+        <v>38</v>
+      </c>
+      <c r="F227" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G227" s="4" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="228" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B228" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C228">
         <v>14</v>
       </c>
       <c r="D228" s="1" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="E228" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F228" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G228" s="8" t="s">
-        <v>31</v>
+        <v>38</v>
+      </c>
+      <c r="F228" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G228" s="4" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="229" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A229" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B229" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C229">
         <v>14</v>
       </c>
       <c r="D229" s="1" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="E229" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F229" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G229" s="8" t="s">
-        <v>33</v>
+        <v>21</v>
+      </c>
+      <c r="F229" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G229" s="4" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="230" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A230" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B230" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C230">
         <v>14</v>
       </c>
       <c r="D230" s="1" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="E230" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F230" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="G230" s="8" t="s">
-        <v>34</v>
+        <v>39</v>
+      </c>
+      <c r="F230" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G230" s="4" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="231" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A231" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B231" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C231">
         <v>14</v>
       </c>
       <c r="D231" s="1" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="E231" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F231" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="F231" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G231" s="4" t="s">
         <v>28</v>
-      </c>
-      <c r="G231" s="8" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="232" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A232" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B232" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C232">
         <v>14</v>
       </c>
       <c r="D232" s="1" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="E232" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F232" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G232" s="4" t="s">
         <v>27</v>
-      </c>
-      <c r="F232" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="G232" s="8" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="233" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A233" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B233" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C233">
         <v>14</v>
       </c>
       <c r="D233" s="1" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="E233" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F233" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G233" s="8" t="s">
-        <v>31</v>
+        <v>38</v>
+      </c>
+      <c r="F233" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G233" s="4" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="234" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A234" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B234" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C234">
         <v>14</v>
       </c>
       <c r="D234" s="1" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="E234" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F234" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="G234" s="8" t="s">
-        <v>35</v>
+        <v>38</v>
+      </c>
+      <c r="F234" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="G234" s="4" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="235" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A235" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B235" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C235">
         <v>14</v>
       </c>
       <c r="D235" s="1" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="E235" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F235" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="G235" s="8" t="s">
-        <v>33</v>
+        <v>21</v>
+      </c>
+      <c r="F235" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="G235" s="4" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="236" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A236" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B236" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C236">
         <v>14</v>
       </c>
       <c r="D236" s="1" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="E236" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F236" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G236" s="4" t="s">
         <v>27</v>
-      </c>
-      <c r="F236" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G236" s="8" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="237" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A237" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B237" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C237">
         <v>14</v>
       </c>
       <c r="D237" s="1" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="E237" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="F237" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="G237" s="8" t="s">
-        <v>39</v>
+        <v>44</v>
+      </c>
+      <c r="F237" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G237" s="4" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="238" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A238" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B238" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C238">
         <v>14</v>
       </c>
       <c r="D238" s="1" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="E238" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F238" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G238" s="8" t="s">
-        <v>35</v>
+        <v>38</v>
+      </c>
+      <c r="F238" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G238" s="4" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="239" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A239" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B239" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C239">
         <v>14</v>
       </c>
       <c r="D239" s="1" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="E239" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F239" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="G239" s="8" t="s">
-        <v>29</v>
+        <v>39</v>
+      </c>
+      <c r="F239" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G239" s="4" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="240" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D240" s="1"/>
       <c r="E240" s="1"/>
-      <c r="F240" s="8"/>
-      <c r="G240" s="8"/>
+      <c r="F240" s="4"/>
+      <c r="G240" s="4"/>
     </row>
     <row r="241" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D241" s="1"/>
       <c r="E241" s="1"/>
-      <c r="F241" s="8"/>
-      <c r="G241" s="8"/>
+      <c r="F241" s="4"/>
+      <c r="G241" s="4"/>
     </row>
     <row r="242" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D242" s="1"/>
       <c r="E242" s="1"/>
-      <c r="F242" s="8"/>
-      <c r="G242" s="8"/>
+      <c r="F242" s="4"/>
+      <c r="G242" s="4"/>
     </row>
     <row r="243" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D243" s="1"/>
       <c r="E243" s="1"/>
-      <c r="F243" s="8"/>
-      <c r="G243" s="8"/>
+      <c r="F243" s="4"/>
+      <c r="G243" s="4"/>
     </row>
     <row r="244" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D244" s="1"/>
       <c r="E244" s="1"/>
-      <c r="F244" s="8"/>
-      <c r="G244" s="8"/>
+      <c r="F244" s="4"/>
+      <c r="G244" s="4"/>
     </row>
     <row r="245" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D245" s="1"/>
       <c r="E245" s="1"/>
-      <c r="F245" s="8"/>
-      <c r="G245" s="8"/>
+      <c r="F245" s="4"/>
+      <c r="G245" s="4"/>
     </row>
     <row r="246" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D246" s="1"/>
       <c r="E246" s="1"/>
-      <c r="F246" s="8"/>
-      <c r="G246" s="8"/>
+      <c r="F246" s="4"/>
+      <c r="G246" s="4"/>
     </row>
     <row r="247" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D247" s="1"/>
       <c r="E247" s="1"/>
-      <c r="F247" s="8"/>
-      <c r="G247" s="8"/>
+      <c r="F247" s="4"/>
+      <c r="G247" s="4"/>
     </row>
     <row r="248" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D248" s="1"/>
       <c r="E248" s="1"/>
-      <c r="F248" s="8"/>
-      <c r="G248" s="8"/>
+      <c r="F248" s="4"/>
+      <c r="G248" s="4"/>
     </row>
     <row r="249" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D249" s="1"/>
       <c r="E249" s="1"/>
-      <c r="F249" s="8"/>
-      <c r="G249" s="8"/>
+      <c r="F249" s="4"/>
+      <c r="G249" s="4"/>
     </row>
     <row r="250" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D250" s="1"/>
       <c r="E250" s="1"/>
-      <c r="F250" s="8"/>
-      <c r="G250" s="8"/>
+      <c r="F250" s="4"/>
+      <c r="G250" s="4"/>
     </row>
     <row r="251" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D251" s="1"/>
       <c r="E251" s="1"/>
-      <c r="F251" s="8"/>
-      <c r="G251" s="8"/>
+      <c r="F251" s="4"/>
+      <c r="G251" s="4"/>
     </row>
     <row r="252" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D252" s="1"/>
       <c r="E252" s="1"/>
-      <c r="F252" s="8"/>
-      <c r="G252" s="8"/>
+      <c r="F252" s="4"/>
+      <c r="G252" s="4"/>
     </row>
     <row r="253" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D253" s="1"/>
       <c r="E253" s="1"/>
-      <c r="F253" s="8"/>
-      <c r="G253" s="8"/>
+      <c r="F253" s="4"/>
+      <c r="G253" s="4"/>
     </row>
     <row r="254" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D254" s="1"/>
       <c r="E254" s="1"/>
-      <c r="F254" s="8"/>
-      <c r="G254" s="8"/>
+      <c r="F254" s="4"/>
+      <c r="G254" s="4"/>
     </row>
     <row r="255" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D255" s="1"/>
       <c r="E255" s="1"/>
-      <c r="F255" s="8"/>
-      <c r="G255" s="8"/>
+      <c r="F255" s="4"/>
+      <c r="G255" s="4"/>
     </row>
     <row r="256" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D256" s="1"/>
       <c r="E256" s="1"/>
-      <c r="F256" s="8"/>
-      <c r="G256" s="8"/>
+      <c r="F256" s="4"/>
+      <c r="G256" s="4"/>
     </row>
     <row r="257" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D257" s="1"/>
       <c r="E257" s="1"/>
-      <c r="F257" s="8"/>
-      <c r="G257" s="8"/>
+      <c r="F257" s="4"/>
+      <c r="G257" s="4"/>
     </row>
     <row r="258" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D258" s="1"/>
       <c r="E258" s="1"/>
-      <c r="F258" s="8"/>
-      <c r="G258" s="8"/>
+      <c r="F258" s="4"/>
+      <c r="G258" s="4"/>
     </row>
     <row r="259" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D259" s="1"/>
       <c r="E259" s="1"/>
-      <c r="F259" s="8"/>
-      <c r="G259" s="8"/>
+      <c r="F259" s="4"/>
+      <c r="G259" s="4"/>
     </row>
     <row r="260" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D260" s="1"/>
       <c r="E260" s="1"/>
-      <c r="F260" s="8"/>
-      <c r="G260" s="8"/>
+      <c r="F260" s="4"/>
+      <c r="G260" s="4"/>
     </row>
     <row r="261" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D261" s="1"/>
       <c r="E261" s="1"/>
-      <c r="F261" s="8"/>
-      <c r="G261" s="8"/>
+      <c r="F261" s="4"/>
+      <c r="G261" s="4"/>
     </row>
     <row r="262" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D262" s="1"/>
       <c r="E262" s="1"/>
-      <c r="F262" s="8"/>
-      <c r="G262" s="8"/>
+      <c r="F262" s="4"/>
+      <c r="G262" s="4"/>
     </row>
     <row r="263" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D263" s="1"/>
       <c r="E263" s="1"/>
-      <c r="F263" s="8"/>
-      <c r="G263" s="8"/>
+      <c r="F263" s="4"/>
+      <c r="G263" s="4"/>
     </row>
     <row r="264" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D264" s="1"/>
       <c r="E264" s="1"/>
-      <c r="F264" s="8"/>
-      <c r="G264" s="8"/>
+      <c r="F264" s="4"/>
+      <c r="G264" s="4"/>
     </row>
     <row r="265" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D265" s="1"/>
       <c r="E265" s="1"/>
-      <c r="F265" s="8"/>
-      <c r="G265" s="8"/>
+      <c r="F265" s="4"/>
+      <c r="G265" s="4"/>
     </row>
     <row r="266" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D266" s="1"/>
       <c r="E266" s="1"/>
-      <c r="F266" s="8"/>
-      <c r="G266" s="8"/>
+      <c r="F266" s="4"/>
+      <c r="G266" s="4"/>
     </row>
     <row r="267" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D267" s="1"/>
       <c r="E267" s="1"/>
-      <c r="F267" s="8"/>
-      <c r="G267" s="8"/>
+      <c r="F267" s="4"/>
+      <c r="G267" s="4"/>
     </row>
     <row r="268" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D268" s="1"/>
       <c r="E268" s="1"/>
-      <c r="F268" s="8"/>
-      <c r="G268" s="8"/>
+      <c r="F268" s="4"/>
+      <c r="G268" s="4"/>
     </row>
     <row r="269" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D269" s="1"/>
       <c r="E269" s="1"/>
-      <c r="F269" s="8"/>
-      <c r="G269" s="8"/>
+      <c r="F269" s="4"/>
+      <c r="G269" s="4"/>
     </row>
     <row r="270" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D270" s="1"/>
       <c r="E270" s="1"/>
-      <c r="F270" s="8"/>
-      <c r="G270" s="8"/>
+      <c r="F270" s="4"/>
+      <c r="G270" s="4"/>
     </row>
     <row r="271" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D271" s="1"/>
       <c r="E271" s="1"/>
-      <c r="F271" s="8"/>
-      <c r="G271" s="8"/>
+      <c r="F271" s="4"/>
+      <c r="G271" s="4"/>
     </row>
     <row r="272" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D272" s="1"/>
       <c r="E272" s="1"/>
-      <c r="F272" s="8"/>
-      <c r="G272" s="8"/>
+      <c r="F272" s="4"/>
+      <c r="G272" s="4"/>
     </row>
     <row r="273" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D273" s="1"/>
       <c r="E273" s="1"/>
-      <c r="F273" s="8"/>
-      <c r="G273" s="8"/>
+      <c r="F273" s="4"/>
+      <c r="G273" s="4"/>
     </row>
     <row r="274" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D274" s="1"/>
       <c r="E274" s="1"/>
-      <c r="F274" s="8"/>
-      <c r="G274" s="8"/>
+      <c r="F274" s="4"/>
+      <c r="G274" s="4"/>
     </row>
     <row r="275" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D275" s="1"/>
       <c r="E275" s="1"/>
-      <c r="F275" s="8"/>
-      <c r="G275" s="8"/>
+      <c r="F275" s="4"/>
+      <c r="G275" s="4"/>
     </row>
     <row r="276" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D276" s="1"/>
       <c r="E276" s="1"/>
-      <c r="F276" s="8"/>
-      <c r="G276" s="8"/>
+      <c r="F276" s="4"/>
+      <c r="G276" s="4"/>
     </row>
     <row r="277" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D277" s="1"/>
       <c r="E277" s="1"/>
-      <c r="F277" s="8"/>
-      <c r="G277" s="8"/>
+      <c r="F277" s="4"/>
+      <c r="G277" s="4"/>
     </row>
     <row r="278" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D278" s="1"/>
       <c r="E278" s="1"/>
-      <c r="F278" s="8"/>
-      <c r="G278" s="8"/>
+      <c r="F278" s="4"/>
+      <c r="G278" s="4"/>
     </row>
     <row r="279" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D279" s="1"/>
       <c r="E279" s="1"/>
-      <c r="F279" s="8"/>
-      <c r="G279" s="8"/>
+      <c r="F279" s="4"/>
+      <c r="G279" s="4"/>
     </row>
     <row r="280" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D280" s="1"/>
       <c r="E280" s="1"/>
-      <c r="F280" s="8"/>
-      <c r="G280" s="8"/>
+      <c r="F280" s="4"/>
+      <c r="G280" s="4"/>
     </row>
     <row r="281" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D281" s="1"/>
       <c r="E281" s="1"/>
-      <c r="F281" s="8"/>
-      <c r="G281" s="8"/>
+      <c r="F281" s="4"/>
+      <c r="G281" s="4"/>
     </row>
     <row r="282" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D282" s="1"/>
       <c r="E282" s="1"/>
-      <c r="F282" s="8"/>
-      <c r="G282" s="8"/>
+      <c r="F282" s="4"/>
+      <c r="G282" s="4"/>
     </row>
     <row r="283" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D283" s="1"/>
       <c r="E283" s="1"/>
-      <c r="F283" s="8"/>
-      <c r="G283" s="8"/>
+      <c r="F283" s="4"/>
+      <c r="G283" s="4"/>
     </row>
     <row r="284" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D284" s="1"/>
       <c r="E284" s="1"/>
-      <c r="F284" s="8"/>
-      <c r="G284" s="8"/>
+      <c r="F284" s="4"/>
+      <c r="G284" s="4"/>
     </row>
     <row r="285" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D285" s="1"/>
       <c r="E285" s="1"/>
-      <c r="F285" s="8"/>
-      <c r="G285" s="8"/>
+      <c r="F285" s="4"/>
+      <c r="G285" s="4"/>
     </row>
     <row r="286" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D286" s="1"/>
       <c r="E286" s="1"/>
-      <c r="F286" s="8"/>
-      <c r="G286" s="8"/>
+      <c r="F286" s="4"/>
+      <c r="G286" s="4"/>
     </row>
     <row r="287" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D287" s="1"/>
       <c r="E287" s="1"/>
-      <c r="F287" s="8"/>
-      <c r="G287" s="8"/>
+      <c r="F287" s="4"/>
+      <c r="G287" s="4"/>
     </row>
     <row r="288" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D288" s="1"/>
       <c r="E288" s="1"/>
-      <c r="F288" s="8"/>
-      <c r="G288" s="8"/>
+      <c r="F288" s="4"/>
+      <c r="G288" s="4"/>
     </row>
     <row r="289" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D289" s="1"/>
       <c r="E289" s="1"/>
-      <c r="F289" s="8"/>
-      <c r="G289" s="8"/>
+      <c r="F289" s="4"/>
+      <c r="G289" s="4"/>
     </row>
     <row r="290" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D290" s="1"/>
       <c r="E290" s="1"/>
-      <c r="F290" s="8"/>
-      <c r="G290" s="8"/>
+      <c r="F290" s="4"/>
+      <c r="G290" s="4"/>
     </row>
     <row r="291" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D291" s="1"/>
       <c r="E291" s="1"/>
-      <c r="F291" s="8"/>
-      <c r="G291" s="8"/>
+      <c r="F291" s="4"/>
+      <c r="G291" s="4"/>
     </row>
     <row r="292" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D292" s="1"/>
       <c r="E292" s="1"/>
-      <c r="F292" s="8"/>
-      <c r="G292" s="8"/>
+      <c r="F292" s="4"/>
+      <c r="G292" s="4"/>
     </row>
     <row r="293" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D293" s="1"/>
       <c r="E293" s="1"/>
-      <c r="F293" s="8"/>
-      <c r="G293" s="8"/>
+      <c r="F293" s="4"/>
+      <c r="G293" s="4"/>
     </row>
     <row r="294" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D294" s="1"/>
       <c r="E294" s="1"/>
-      <c r="F294" s="8"/>
-      <c r="G294" s="8"/>
+      <c r="F294" s="4"/>
+      <c r="G294" s="4"/>
     </row>
     <row r="295" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D295" s="1"/>
       <c r="E295" s="1"/>
-      <c r="F295" s="8"/>
-      <c r="G295" s="8"/>
+      <c r="F295" s="4"/>
+      <c r="G295" s="4"/>
     </row>
     <row r="296" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D296" s="1"/>
       <c r="E296" s="1"/>
-      <c r="F296" s="8"/>
-      <c r="G296" s="8"/>
+      <c r="F296" s="4"/>
+      <c r="G296" s="4"/>
     </row>
     <row r="297" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D297" s="1"/>
       <c r="E297" s="1"/>
-      <c r="F297" s="8"/>
-      <c r="G297" s="8"/>
+      <c r="F297" s="4"/>
+      <c r="G297" s="4"/>
     </row>
     <row r="298" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D298" s="1"/>
       <c r="E298" s="1"/>
-      <c r="F298" s="8"/>
-      <c r="G298" s="8"/>
+      <c r="F298" s="4"/>
+      <c r="G298" s="4"/>
     </row>
     <row r="299" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D299" s="1"/>
       <c r="E299" s="1"/>
-      <c r="F299" s="8"/>
-      <c r="G299" s="8"/>
+      <c r="F299" s="4"/>
+      <c r="G299" s="4"/>
     </row>
     <row r="300" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D300" s="1"/>
       <c r="E300" s="1"/>
-      <c r="F300" s="8"/>
-      <c r="G300" s="8"/>
+      <c r="F300" s="4"/>
+      <c r="G300" s="4"/>
     </row>
     <row r="301" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D301" s="1"/>
       <c r="E301" s="1"/>
-      <c r="F301" s="8"/>
-      <c r="G301" s="8"/>
+      <c r="F301" s="4"/>
+      <c r="G301" s="4"/>
     </row>
     <row r="302" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D302" s="1"/>
       <c r="E302" s="1"/>
-      <c r="F302" s="8"/>
-      <c r="G302" s="8"/>
+      <c r="F302" s="4"/>
+      <c r="G302" s="4"/>
     </row>
     <row r="303" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D303" s="1"/>
       <c r="E303" s="1"/>
-      <c r="F303" s="8"/>
-      <c r="G303" s="8"/>
+      <c r="F303" s="4"/>
+      <c r="G303" s="4"/>
     </row>
     <row r="304" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D304" s="1"/>
       <c r="E304" s="1"/>
-      <c r="F304" s="8"/>
-      <c r="G304" s="8"/>
+      <c r="F304" s="4"/>
+      <c r="G304" s="4"/>
     </row>
     <row r="305" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D305" s="1"/>
       <c r="E305" s="1"/>
-      <c r="F305" s="8"/>
-      <c r="G305" s="8"/>
+      <c r="F305" s="4"/>
+      <c r="G305" s="4"/>
     </row>
     <row r="306" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D306" s="1"/>
       <c r="E306" s="1"/>
-      <c r="F306" s="8"/>
-      <c r="G306" s="8"/>
+      <c r="F306" s="4"/>
+      <c r="G306" s="4"/>
     </row>
     <row r="307" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D307" s="1"/>
       <c r="E307" s="1"/>
-      <c r="F307" s="8"/>
-      <c r="G307" s="8"/>
+      <c r="F307" s="4"/>
+      <c r="G307" s="4"/>
     </row>
     <row r="308" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D308" s="1"/>
       <c r="E308" s="1"/>
-      <c r="F308" s="8"/>
-      <c r="G308" s="8"/>
+      <c r="F308" s="4"/>
+      <c r="G308" s="4"/>
     </row>
     <row r="309" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D309" s="1"/>
       <c r="E309" s="1"/>
-      <c r="F309" s="8"/>
-      <c r="G309" s="8"/>
+      <c r="F309" s="4"/>
+      <c r="G309" s="4"/>
     </row>
     <row r="310" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D310" s="1"/>
       <c r="E310" s="1"/>
-      <c r="F310" s="8"/>
-      <c r="G310" s="8"/>
+      <c r="F310" s="4"/>
+      <c r="G310" s="4"/>
     </row>
     <row r="311" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D311" s="1"/>
       <c r="E311" s="1"/>
-      <c r="F311" s="8"/>
-      <c r="G311" s="8"/>
+      <c r="F311" s="4"/>
+      <c r="G311" s="4"/>
     </row>
     <row r="312" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D312" s="1"/>
       <c r="E312" s="1"/>
-      <c r="F312" s="8"/>
-      <c r="G312" s="8"/>
+      <c r="F312" s="4"/>
+      <c r="G312" s="4"/>
     </row>
     <row r="313" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D313" s="1"/>
       <c r="E313" s="1"/>
-      <c r="F313" s="8"/>
-      <c r="G313" s="8"/>
+      <c r="F313" s="4"/>
+      <c r="G313" s="4"/>
     </row>
     <row r="314" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D314" s="1"/>
       <c r="E314" s="1"/>
-      <c r="F314" s="8"/>
-      <c r="G314" s="8"/>
+      <c r="F314" s="4"/>
+      <c r="G314" s="4"/>
     </row>
     <row r="315" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D315" s="1"/>
       <c r="E315" s="1"/>
-      <c r="F315" s="8"/>
-      <c r="G315" s="8"/>
+      <c r="F315" s="4"/>
+      <c r="G315" s="4"/>
     </row>
     <row r="316" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D316" s="1"/>
       <c r="E316" s="1"/>
-      <c r="F316" s="8"/>
-      <c r="G316" s="8"/>
+      <c r="F316" s="4"/>
+      <c r="G316" s="4"/>
     </row>
     <row r="317" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D317" s="1"/>
       <c r="E317" s="1"/>
-      <c r="F317" s="8"/>
-      <c r="G317" s="8"/>
+      <c r="F317" s="4"/>
+      <c r="G317" s="4"/>
     </row>
     <row r="318" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D318" s="1"/>
       <c r="E318" s="1"/>
-      <c r="F318" s="8"/>
-      <c r="G318" s="8"/>
+      <c r="F318" s="4"/>
+      <c r="G318" s="4"/>
     </row>
     <row r="319" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D319" s="1"/>
       <c r="E319" s="1"/>
-      <c r="F319" s="8"/>
-      <c r="G319" s="8"/>
+      <c r="F319" s="4"/>
+      <c r="G319" s="4"/>
     </row>
     <row r="320" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D320" s="1"/>
       <c r="E320" s="1"/>
-      <c r="F320" s="8"/>
-      <c r="G320" s="8"/>
+      <c r="F320" s="4"/>
+      <c r="G320" s="4"/>
     </row>
     <row r="321" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D321" s="1"/>
       <c r="E321" s="1"/>
-      <c r="F321" s="8"/>
-      <c r="G321" s="8"/>
+      <c r="F321" s="4"/>
+      <c r="G321" s="4"/>
     </row>
     <row r="322" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D322" s="1"/>
       <c r="E322" s="1"/>
-      <c r="F322" s="8"/>
-      <c r="G322" s="8"/>
+      <c r="F322" s="4"/>
+      <c r="G322" s="4"/>
     </row>
     <row r="323" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D323" s="1"/>
       <c r="E323" s="1"/>
-      <c r="F323" s="8"/>
-      <c r="G323" s="8"/>
+      <c r="F323" s="4"/>
+      <c r="G323" s="4"/>
     </row>
     <row r="324" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D324" s="1"/>
       <c r="E324" s="1"/>
-      <c r="F324" s="8"/>
-      <c r="G324" s="8"/>
+      <c r="F324" s="4"/>
+      <c r="G324" s="4"/>
     </row>
     <row r="325" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D325" s="1"/>
       <c r="E325" s="1"/>
-      <c r="F325" s="8"/>
-      <c r="G325" s="8"/>
+      <c r="F325" s="4"/>
+      <c r="G325" s="4"/>
     </row>
     <row r="326" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D326" s="1"/>
       <c r="E326" s="1"/>
-      <c r="F326" s="8"/>
-      <c r="G326" s="8"/>
+      <c r="F326" s="4"/>
+      <c r="G326" s="4"/>
     </row>
     <row r="327" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D327" s="1"/>
       <c r="E327" s="1"/>
-      <c r="F327" s="8"/>
-      <c r="G327" s="8"/>
+      <c r="F327" s="4"/>
+      <c r="G327" s="4"/>
     </row>
     <row r="328" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D328" s="1"/>
       <c r="E328" s="1"/>
-      <c r="F328" s="8"/>
-      <c r="G328" s="8"/>
+      <c r="F328" s="4"/>
+      <c r="G328" s="4"/>
     </row>
     <row r="329" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D329" s="1"/>
       <c r="E329" s="1"/>
-      <c r="F329" s="8"/>
-      <c r="G329" s="8"/>
+      <c r="F329" s="4"/>
+      <c r="G329" s="4"/>
     </row>
     <row r="330" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D330" s="1"/>
       <c r="E330" s="1"/>
-      <c r="F330" s="8"/>
-      <c r="G330" s="8"/>
+      <c r="F330" s="4"/>
+      <c r="G330" s="4"/>
     </row>
     <row r="331" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D331" s="1"/>
       <c r="E331" s="1"/>
-      <c r="F331" s="8"/>
-      <c r="G331" s="8"/>
+      <c r="F331" s="4"/>
+      <c r="G331" s="4"/>
     </row>
     <row r="332" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D332" s="1"/>
       <c r="E332" s="1"/>
-      <c r="F332" s="8"/>
-      <c r="G332" s="8"/>
+      <c r="F332" s="4"/>
+      <c r="G332" s="4"/>
     </row>
     <row r="333" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D333" s="1"/>
       <c r="E333" s="1"/>
-      <c r="F333" s="8"/>
-      <c r="G333" s="8"/>
+      <c r="F333" s="4"/>
+      <c r="G333" s="4"/>
     </row>
     <row r="334" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D334" s="1"/>
       <c r="E334" s="1"/>
-      <c r="F334" s="8"/>
-      <c r="G334" s="8"/>
+      <c r="F334" s="4"/>
+      <c r="G334" s="4"/>
     </row>
     <row r="335" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D335" s="1"/>
       <c r="E335" s="1"/>
-      <c r="F335" s="8"/>
-      <c r="G335" s="8"/>
+      <c r="F335" s="4"/>
+      <c r="G335" s="4"/>
     </row>
     <row r="336" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D336" s="1"/>
       <c r="E336" s="1"/>
-      <c r="F336" s="8"/>
-      <c r="G336" s="8"/>
+      <c r="F336" s="4"/>
+      <c r="G336" s="4"/>
     </row>
     <row r="337" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D337" s="1"/>
       <c r="E337" s="1"/>
-      <c r="F337" s="8"/>
-      <c r="G337" s="8"/>
+      <c r="F337" s="4"/>
+      <c r="G337" s="4"/>
     </row>
     <row r="338" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D338" s="1"/>
       <c r="E338" s="1"/>
-      <c r="F338" s="8"/>
-      <c r="G338" s="8"/>
+      <c r="F338" s="4"/>
+      <c r="G338" s="4"/>
     </row>
     <row r="339" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D339" s="1"/>
       <c r="E339" s="1"/>
-      <c r="F339" s="8"/>
-      <c r="G339" s="8"/>
+      <c r="F339" s="4"/>
+      <c r="G339" s="4"/>
     </row>
     <row r="340" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D340" s="1"/>
       <c r="E340" s="1"/>
-      <c r="F340" s="8"/>
-      <c r="G340" s="8"/>
+      <c r="F340" s="4"/>
+      <c r="G340" s="4"/>
     </row>
     <row r="341" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D341" s="1"/>
       <c r="E341" s="1"/>
-      <c r="F341" s="8"/>
-      <c r="G341" s="8"/>
+      <c r="F341" s="4"/>
+      <c r="G341" s="4"/>
     </row>
     <row r="342" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D342" s="1"/>
       <c r="E342" s="1"/>
-      <c r="F342" s="8"/>
-      <c r="G342" s="8"/>
+      <c r="F342" s="4"/>
+      <c r="G342" s="4"/>
     </row>
     <row r="343" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D343" s="1"/>
       <c r="E343" s="1"/>
-      <c r="F343" s="8"/>
-      <c r="G343" s="8"/>
+      <c r="F343" s="4"/>
+      <c r="G343" s="4"/>
     </row>
     <row r="344" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D344" s="1"/>
       <c r="E344" s="1"/>
-      <c r="F344" s="8"/>
-      <c r="G344" s="8"/>
+      <c r="F344" s="4"/>
+      <c r="G344" s="4"/>
     </row>
     <row r="345" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D345" s="1"/>
       <c r="E345" s="1"/>
-      <c r="F345" s="8"/>
-      <c r="G345" s="8"/>
+      <c r="F345" s="4"/>
+      <c r="G345" s="4"/>
     </row>
     <row r="346" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D346" s="1"/>
       <c r="E346" s="1"/>
-      <c r="F346" s="8"/>
-      <c r="G346" s="8"/>
+      <c r="F346" s="4"/>
+      <c r="G346" s="4"/>
     </row>
     <row r="347" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D347" s="1"/>
       <c r="E347" s="1"/>
-      <c r="F347" s="8"/>
-      <c r="G347" s="8"/>
+      <c r="F347" s="4"/>
+      <c r="G347" s="4"/>
     </row>
     <row r="348" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D348" s="1"/>
       <c r="E348" s="1"/>
-      <c r="F348" s="8"/>
-      <c r="G348" s="8"/>
+      <c r="F348" s="4"/>
+      <c r="G348" s="4"/>
     </row>
     <row r="349" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D349" s="1"/>
       <c r="E349" s="1"/>
-      <c r="F349" s="8"/>
-      <c r="G349" s="8"/>
+      <c r="F349" s="4"/>
+      <c r="G349" s="4"/>
     </row>
     <row r="350" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D350" s="1"/>
       <c r="E350" s="1"/>
-      <c r="F350" s="8"/>
-      <c r="G350" s="8"/>
+      <c r="F350" s="4"/>
+      <c r="G350" s="4"/>
     </row>
     <row r="351" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D351" s="1"/>
       <c r="E351" s="1"/>
-      <c r="F351" s="8"/>
-      <c r="G351" s="8"/>
+      <c r="F351" s="4"/>
+      <c r="G351" s="4"/>
     </row>
     <row r="352" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D352" s="1"/>
       <c r="E352" s="1"/>
-      <c r="F352" s="8"/>
-      <c r="G352" s="8"/>
+      <c r="F352" s="4"/>
+      <c r="G352" s="4"/>
     </row>
     <row r="353" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D353" s="1"/>
       <c r="E353" s="1"/>
-      <c r="F353" s="8"/>
-      <c r="G353" s="8"/>
+      <c r="F353" s="4"/>
+      <c r="G353" s="4"/>
     </row>
     <row r="354" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D354" s="1"/>
       <c r="E354" s="1"/>
-      <c r="F354" s="8"/>
-      <c r="G354" s="8"/>
+      <c r="F354" s="4"/>
+      <c r="G354" s="4"/>
     </row>
     <row r="355" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D355" s="1"/>
       <c r="E355" s="1"/>
-      <c r="F355" s="8"/>
-      <c r="G355" s="8"/>
+      <c r="F355" s="4"/>
+      <c r="G355" s="4"/>
     </row>
     <row r="356" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D356" s="1"/>
       <c r="E356" s="1"/>
-      <c r="F356" s="8"/>
-      <c r="G356" s="8"/>
+      <c r="F356" s="4"/>
+      <c r="G356" s="4"/>
     </row>
     <row r="357" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D357" s="1"/>
       <c r="E357" s="1"/>
-      <c r="F357" s="8"/>
-      <c r="G357" s="8"/>
+      <c r="F357" s="4"/>
+      <c r="G357" s="4"/>
     </row>
     <row r="358" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D358" s="1"/>
       <c r="E358" s="1"/>
-      <c r="F358" s="8"/>
-      <c r="G358" s="8"/>
+      <c r="F358" s="4"/>
+      <c r="G358" s="4"/>
     </row>
     <row r="359" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D359" s="1"/>
       <c r="E359" s="1"/>
-      <c r="F359" s="8"/>
-      <c r="G359" s="8"/>
+      <c r="F359" s="4"/>
+      <c r="G359" s="4"/>
     </row>
     <row r="360" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D360" s="1"/>
       <c r="E360" s="1"/>
-      <c r="F360" s="8"/>
-      <c r="G360" s="8"/>
+      <c r="F360" s="4"/>
+      <c r="G360" s="4"/>
     </row>
     <row r="361" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D361" s="1"/>
       <c r="E361" s="1"/>
-      <c r="F361" s="8"/>
-      <c r="G361" s="8"/>
+      <c r="F361" s="4"/>
+      <c r="G361" s="4"/>
     </row>
     <row r="362" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D362" s="1"/>
       <c r="E362" s="1"/>
-      <c r="F362" s="8"/>
-      <c r="G362" s="8"/>
+      <c r="F362" s="4"/>
+      <c r="G362" s="4"/>
     </row>
     <row r="363" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D363" s="1"/>
       <c r="E363" s="1"/>
-      <c r="F363" s="8"/>
-      <c r="G363" s="8"/>
+      <c r="F363" s="4"/>
+      <c r="G363" s="4"/>
     </row>
     <row r="364" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D364" s="1"/>
       <c r="E364" s="1"/>
-      <c r="F364" s="8"/>
-      <c r="G364" s="8"/>
+      <c r="F364" s="4"/>
+      <c r="G364" s="4"/>
     </row>
     <row r="365" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D365" s="1"/>
       <c r="E365" s="1"/>
-      <c r="F365" s="8"/>
-      <c r="G365" s="8"/>
+      <c r="F365" s="4"/>
+      <c r="G365" s="4"/>
     </row>
     <row r="366" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D366" s="1"/>
       <c r="E366" s="1"/>
-      <c r="F366" s="8"/>
-      <c r="G366" s="8"/>
+      <c r="F366" s="4"/>
+      <c r="G366" s="4"/>
     </row>
     <row r="367" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D367" s="1"/>
       <c r="E367" s="1"/>
-      <c r="F367" s="8"/>
-      <c r="G367" s="8"/>
+      <c r="F367" s="4"/>
+      <c r="G367" s="4"/>
     </row>
     <row r="368" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D368" s="1"/>
       <c r="E368" s="1"/>
-      <c r="F368" s="8"/>
-      <c r="G368" s="8"/>
+      <c r="F368" s="4"/>
+      <c r="G368" s="4"/>
     </row>
     <row r="369" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D369" s="1"/>
       <c r="E369" s="1"/>
-      <c r="F369" s="8"/>
-      <c r="G369" s="8"/>
+      <c r="F369" s="4"/>
+      <c r="G369" s="4"/>
     </row>
     <row r="370" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D370" s="1"/>
       <c r="E370" s="1"/>
-      <c r="F370" s="8"/>
-      <c r="G370" s="8"/>
+      <c r="F370" s="4"/>
+      <c r="G370" s="4"/>
     </row>
     <row r="371" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D371" s="1"/>
       <c r="E371" s="1"/>
-      <c r="F371" s="8"/>
-      <c r="G371" s="8"/>
+      <c r="F371" s="4"/>
+      <c r="G371" s="4"/>
     </row>
     <row r="372" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D372" s="1"/>
       <c r="E372" s="1"/>
-      <c r="F372" s="8"/>
-      <c r="G372" s="8"/>
+      <c r="F372" s="4"/>
+      <c r="G372" s="4"/>
     </row>
     <row r="373" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D373" s="1"/>
       <c r="E373" s="1"/>
-      <c r="F373" s="8"/>
-      <c r="G373" s="8"/>
+      <c r="F373" s="4"/>
+      <c r="G373" s="4"/>
     </row>
     <row r="374" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D374" s="1"/>
       <c r="E374" s="1"/>
-      <c r="F374" s="8"/>
-      <c r="G374" s="8"/>
+      <c r="F374" s="4"/>
+      <c r="G374" s="4"/>
     </row>
     <row r="375" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D375" s="1"/>
       <c r="E375" s="1"/>
-      <c r="F375" s="8"/>
-      <c r="G375" s="8"/>
+      <c r="F375" s="4"/>
+      <c r="G375" s="4"/>
     </row>
     <row r="376" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D376" s="1"/>
       <c r="E376" s="1"/>
-      <c r="F376" s="8"/>
-      <c r="G376" s="8"/>
+      <c r="F376" s="4"/>
+      <c r="G376" s="4"/>
     </row>
     <row r="377" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D377" s="1"/>
       <c r="E377" s="1"/>
-      <c r="F377" s="8"/>
-      <c r="G377" s="8"/>
+      <c r="F377" s="4"/>
+      <c r="G377" s="4"/>
     </row>
     <row r="378" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D378" s="1"/>
       <c r="E378" s="1"/>
-      <c r="F378" s="8"/>
-      <c r="G378" s="8"/>
+      <c r="F378" s="4"/>
+      <c r="G378" s="4"/>
     </row>
     <row r="379" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D379" s="1"/>
       <c r="E379" s="1"/>
-      <c r="F379" s="8"/>
-      <c r="G379" s="8"/>
+      <c r="F379" s="4"/>
+      <c r="G379" s="4"/>
     </row>
     <row r="380" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D380" s="1"/>
       <c r="E380" s="1"/>
-      <c r="F380" s="8"/>
-      <c r="G380" s="8"/>
+      <c r="F380" s="4"/>
+      <c r="G380" s="4"/>
     </row>
     <row r="381" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D381" s="1"/>
       <c r="E381" s="1"/>
-      <c r="F381" s="8"/>
-      <c r="G381" s="8"/>
+      <c r="F381" s="4"/>
+      <c r="G381" s="4"/>
     </row>
     <row r="382" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D382" s="1"/>
       <c r="E382" s="1"/>
-      <c r="F382" s="8"/>
-      <c r="G382" s="8"/>
+      <c r="F382" s="4"/>
+      <c r="G382" s="4"/>
     </row>
     <row r="383" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D383" s="1"/>
       <c r="E383" s="1"/>
-      <c r="F383" s="8"/>
-      <c r="G383" s="8"/>
+      <c r="F383" s="4"/>
+      <c r="G383" s="4"/>
     </row>
     <row r="384" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D384" s="1"/>
       <c r="E384" s="1"/>
-      <c r="F384" s="8"/>
-      <c r="G384" s="8"/>
+      <c r="F384" s="4"/>
+      <c r="G384" s="4"/>
     </row>
     <row r="385" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D385" s="1"/>
       <c r="E385" s="1"/>
-      <c r="F385" s="8"/>
-      <c r="G385" s="8"/>
+      <c r="F385" s="4"/>
+      <c r="G385" s="4"/>
     </row>
     <row r="386" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D386" s="1"/>
       <c r="E386" s="1"/>
-      <c r="F386" s="8"/>
-      <c r="G386" s="8"/>
+      <c r="F386" s="4"/>
+      <c r="G386" s="4"/>
     </row>
     <row r="387" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D387" s="1"/>
       <c r="E387" s="1"/>
-      <c r="F387" s="8"/>
-      <c r="G387" s="8"/>
+      <c r="F387" s="4"/>
+      <c r="G387" s="4"/>
     </row>
     <row r="388" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D388" s="1"/>
       <c r="E388" s="1"/>
-      <c r="F388" s="8"/>
-      <c r="G388" s="8"/>
+      <c r="F388" s="4"/>
+      <c r="G388" s="4"/>
     </row>
     <row r="389" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D389" s="1"/>
       <c r="E389" s="1"/>
-      <c r="F389" s="8"/>
-      <c r="G389" s="8"/>
+      <c r="F389" s="4"/>
+      <c r="G389" s="4"/>
     </row>
     <row r="390" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D390" s="1"/>
       <c r="E390" s="1"/>
-      <c r="F390" s="8"/>
-      <c r="G390" s="8"/>
+      <c r="F390" s="4"/>
+      <c r="G390" s="4"/>
     </row>
     <row r="391" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D391" s="1"/>
       <c r="E391" s="1"/>
-      <c r="F391" s="8"/>
-      <c r="G391" s="8"/>
+      <c r="F391" s="4"/>
+      <c r="G391" s="4"/>
     </row>
     <row r="392" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D392" s="1"/>
       <c r="E392" s="1"/>
-      <c r="F392" s="8"/>
-      <c r="G392" s="8"/>
+      <c r="F392" s="4"/>
+      <c r="G392" s="4"/>
     </row>
     <row r="393" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D393" s="1"/>
       <c r="E393" s="1"/>
-      <c r="F393" s="8"/>
-      <c r="G393" s="8"/>
+      <c r="F393" s="4"/>
+      <c r="G393" s="4"/>
     </row>
     <row r="394" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D394" s="1"/>
       <c r="E394" s="1"/>
-      <c r="F394" s="8"/>
-      <c r="G394" s="8"/>
+      <c r="F394" s="4"/>
+      <c r="G394" s="4"/>
     </row>
     <row r="395" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D395" s="1"/>
       <c r="E395" s="1"/>
-      <c r="F395" s="8"/>
-      <c r="G395" s="8"/>
+      <c r="F395" s="4"/>
+      <c r="G395" s="4"/>
     </row>
     <row r="396" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D396" s="1"/>
       <c r="E396" s="1"/>
-      <c r="F396" s="8"/>
-      <c r="G396" s="8"/>
+      <c r="F396" s="4"/>
+      <c r="G396" s="4"/>
     </row>
     <row r="397" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D397" s="1"/>
       <c r="E397" s="1"/>
-      <c r="F397" s="8"/>
-      <c r="G397" s="8"/>
+      <c r="F397" s="4"/>
+      <c r="G397" s="4"/>
     </row>
     <row r="398" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D398" s="1"/>
       <c r="E398" s="1"/>
-      <c r="F398" s="8"/>
-      <c r="G398" s="8"/>
+      <c r="F398" s="4"/>
+      <c r="G398" s="4"/>
     </row>
     <row r="399" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D399" s="1"/>
       <c r="E399" s="1"/>
-      <c r="F399" s="8"/>
-      <c r="G399" s="8"/>
+      <c r="F399" s="4"/>
+      <c r="G399" s="4"/>
     </row>
     <row r="400" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D400" s="1"/>
       <c r="E400" s="1"/>
-      <c r="F400" s="8"/>
-      <c r="G400" s="8"/>
+      <c r="F400" s="4"/>
+      <c r="G400" s="4"/>
     </row>
     <row r="401" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D401" s="1"/>
       <c r="E401" s="1"/>
-      <c r="F401" s="8"/>
-      <c r="G401" s="8"/>
+      <c r="F401" s="4"/>
+      <c r="G401" s="4"/>
     </row>
     <row r="402" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D402" s="1"/>
       <c r="E402" s="1"/>
-      <c r="F402" s="8"/>
-      <c r="G402" s="8"/>
+      <c r="F402" s="4"/>
+      <c r="G402" s="4"/>
     </row>
     <row r="403" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D403" s="1"/>
       <c r="E403" s="1"/>
-      <c r="F403" s="8"/>
-      <c r="G403" s="8"/>
+      <c r="F403" s="4"/>
+      <c r="G403" s="4"/>
     </row>
     <row r="404" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D404" s="1"/>
       <c r="E404" s="1"/>
-      <c r="F404" s="8"/>
-      <c r="G404" s="8"/>
+      <c r="F404" s="4"/>
+      <c r="G404" s="4"/>
     </row>
     <row r="405" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D405" s="1"/>
       <c r="E405" s="1"/>
-      <c r="F405" s="8"/>
-      <c r="G405" s="8"/>
+      <c r="F405" s="4"/>
+      <c r="G405" s="4"/>
     </row>
     <row r="406" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D406" s="1"/>
       <c r="E406" s="1"/>
-      <c r="F406" s="8"/>
-      <c r="G406" s="8"/>
+      <c r="F406" s="4"/>
+      <c r="G406" s="4"/>
     </row>
     <row r="407" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D407" s="1"/>
       <c r="E407" s="1"/>
-      <c r="F407" s="8"/>
-      <c r="G407" s="8"/>
+      <c r="F407" s="4"/>
+      <c r="G407" s="4"/>
     </row>
     <row r="408" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D408" s="1"/>
       <c r="E408" s="1"/>
-      <c r="F408" s="8"/>
-      <c r="G408" s="8"/>
+      <c r="F408" s="4"/>
+      <c r="G408" s="4"/>
     </row>
     <row r="409" spans="4:7" x14ac:dyDescent="0.3">
       <c r="D409" s="1"/>
       <c r="E409" s="1"/>
-      <c r="F409" s="8"/>
-      <c r="G409" s="8"/>
+      <c r="F409" s="4"/>
+      <c r="G409" s="4"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G409">
